--- a/booking_forms/041_executive_lunch_appointment_form--booking_forms.xlsx
+++ b/booking_forms/041_executive_lunch_appointment_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'office'}</t>
+          <t>office</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'restaurant'}</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'restaurant'}</t>
+          <t>restaurant</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'hotel'}</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'hotel'}</t>
+          <t>hotel</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'valuechartinstance':_11}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'valuechartInstance': 11}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
